--- a/artfynd/A 8691-2026 artfynd.xlsx
+++ b/artfynd/A 8691-2026 artfynd.xlsx
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419457</v>
+        <v>123419461</v>
       </c>
       <c r="B2" t="n">
-        <v>58345</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600852</v>
+        <v>600835</v>
       </c>
       <c r="R2" t="n">
-        <v>6909522</v>
+        <v>6909521</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2186</t>
+          <t>2024_2184</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,9 +781,24 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Källa i granskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granlågor</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Granlågor</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,37 +820,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419461</v>
+        <v>123419459</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,21 +853,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långedalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600835</v>
+        <v>600861</v>
       </c>
       <c r="R3" t="n">
-        <v>6909521</v>
+        <v>6909497</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2184</t>
+          <t>2024_2185</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,11 +926,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Granskog</t>
@@ -933,12 +933,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlågor</t>
+          <t>Stubbar och lågor</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Granlågor</t>
+          <t>Stubbar och lågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -960,32 +960,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419459</v>
+        <v>123419457</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -995,7 +990,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600861</v>
+        <v>600852</v>
       </c>
       <c r="R4" t="n">
-        <v>6909497</v>
+        <v>6909522</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2185</t>
+          <t>2024_2186</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,12 +1054,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hackspår</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,17 +1068,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Stubbar och lågor</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stubbar och lågor</t>
+          <t>Källa i granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1108,12 +1093,7 @@
         <v>123419456</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8691-2026 artfynd.xlsx
+++ b/artfynd/A 8691-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -817,6 +822,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419461</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -957,6 +967,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419459</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1087,6 +1102,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419457</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1217,8 +1237,19 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419456</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>